--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M239"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25405.85</v>
+        <v>25190.68</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18687.74</v>
+        <v>18501.24</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12669.55</v>
+        <v>12543.1</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13467.85</v>
+        <v>13333.44</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17868.92</v>
+        <v>17690.59</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>79030.36</v>
+        <v>78241.62</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15123.26</v>
+        <v>14972.33</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>29025.08</v>
+        <v>28721.13</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11511.05</v>
+        <v>11448.13</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>12757.04</v>
+        <v>12687.32</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13172.13</v>
+        <v>13100.13</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>31090.65</v>
+        <v>30920.39</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7962.4</v>
+        <v>7990.81</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>26836.69</v>
+        <v>27128.58</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>59175.26</v>
+        <v>59818.87</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11066.61</v>
+        <v>11186.97</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14447.87</v>
+        <v>14605.01</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29324.71</v>
+        <v>29643.66</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8609.370000000001</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6999.47</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>20158.82</v>
+        <v>20298.47</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22824.48</v>
+        <v>22982.6</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41504</v>
+        <v>41791.52</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>26661.96</v>
+        <v>26854.18</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5944.24</v>
+        <v>5987.09</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6382.34</v>
+        <v>6371.02</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>58336.15</v>
+        <v>58232.68</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7569</v>
+        <v>7537.8</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8273.52</v>
+        <v>8239.42</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>27528.92</v>
+        <v>27415.46</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>62921.03</v>
+        <v>62823.5</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15141.65</v>
+        <v>15118.18</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24222.29</v>
+        <v>24347.39</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13615.3</v>
+        <v>13685.61</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12841.88</v>
+        <v>12932.51</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12139.48</v>
+        <v>11985.28</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>22102.56</v>
+        <v>21821.81</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8001.17</v>
+        <v>7899.53</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8936.709999999999</v>
+        <v>8904.67</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9240.99</v>
+        <v>9220.99</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8094.55</v>
+        <v>8077.03</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>26317.89</v>
+        <v>26260.93</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>13901.65</v>
+        <v>13871.56</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12803.4</v>
+        <v>12655.22</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>17924.96</v>
+        <v>17717.51</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13644.09</v>
+        <v>13486.18</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>52239.59</v>
+        <v>51797.08</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>20929.69</v>
+        <v>20912.86</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7508.76</v>
+        <v>7537.58</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7615.88</v>
+        <v>7645.11</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7567.22</v>
+        <v>7596.26</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6419.07</v>
+        <v>6443.7</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10740.52</v>
+        <v>10789.19</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>44332.26</v>
+        <v>44533.16</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8316.879999999999</v>
+        <v>8305.209999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>28751.98</v>
+        <v>28788.84</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14002.04</v>
+        <v>14019.99</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>64016.23</v>
+        <v>64098.29</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>77948.14999999999</v>
+        <v>78484.67999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>36753.47</v>
+        <v>37006.46</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7728.43</v>
+        <v>7781.62</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5484.98</v>
+        <v>5531.85</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>27276.81</v>
+        <v>27509.91</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>37043.46</v>
+        <v>37360.03</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>58739.57</v>
+        <v>59369.64</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>64254.38</v>
+        <v>64943.61</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6091.82</v>
+        <v>6157.16</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8141.35</v>
+        <v>8241.4</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>17466.51</v>
+        <v>17562.03</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>63218.68</v>
+        <v>63564.4</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>14235.76</v>
+        <v>14313.62</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9091.52</v>
+        <v>9141.23</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>19182.09</v>
+        <v>19286.99</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>49009.87</v>
+        <v>49277.9</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8665.02</v>
+        <v>8496.02</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7616.64</v>
+        <v>7507.47</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8049.98</v>
+        <v>7933.97</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>24737.91</v>
+        <v>24689.2</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23958.25</v>
+        <v>23911.07</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>16065.98</v>
+        <v>16066.08</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>19027.01</v>
+        <v>19027.13</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11839.25</v>
+        <v>11855.69</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>42223.75</v>
+        <v>42194.91</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>27399.77</v>
+        <v>27381.05</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>50009.4</v>
+        <v>49975.24</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>20770.04</v>
+        <v>20755.85</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7723.86</v>
+        <v>7718.58</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15433.58</v>
+        <v>15380.61</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>29035.98</v>
+        <v>28936.33</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7000.93</v>
+        <v>6963.95</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>66313.67</v>
+        <v>65963.37</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11099.08</v>
+        <v>11029.53</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>37550.49</v>
+        <v>37796.6</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>10893.73</v>
+        <v>11040.43</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>14928.99</v>
+        <v>15156.27</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>24099.27</v>
+        <v>24466.16</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>109064.12</v>
+        <v>111821.26</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>16669.26</v>
+        <v>17090.66</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>57209.18</v>
+        <v>58655.43</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6716.9</v>
+        <v>6886.7</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>23035.75</v>
+        <v>23734.26</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>6708.55</v>
+        <v>6907.95</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>26529.14</v>
+        <v>26434.69</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>20487.68</v>
+        <v>20547.03</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6744.68</v>
+        <v>6764.22</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>48085.11</v>
+        <v>48333.5</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6740.28</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>44990.1</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>40524.21</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>6112.86</v>
+        <v>6168.46</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>31068.69</v>
+        <v>31285</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9839.450000000001</v>
+        <v>9829.309999999999</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>15396.39</v>
+        <v>15286.09</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>34546.47</v>
+        <v>34495.65</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>9310.98</v>
+        <v>9260.280000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>13838.09</v>
+        <v>13756.54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5684-100-CM26</t>
+          <t>1375757-57-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>10846.62</v>
+        <v>38859.55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1375757-57-CM26</t>
+          <t>5684-100-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>39097.12</v>
+        <v>10780.71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1456838-11-CM26</t>
+          <t>1057973-1-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7736,17 +7736,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6726.75</v>
+        <v>13145.81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057973-1-CM26</t>
+          <t>1456838-11-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>13226.18</v>
+        <v>6685.88</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>35519.19</v>
+        <v>35703.08</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>28154.25</v>
+        <v>28181.38</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>28212.27</v>
+        <v>29458.18</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>17856.86</v>
+        <v>18645.45</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>10494.15</v>
+        <v>10798.97</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>43163.45</v>
+        <v>43874.85</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>11368.09</v>
+        <v>11396.06</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>40493.86</v>
+        <v>40593.49</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>20272.95</v>
+        <v>20011.96</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>23054</v>
+        <v>23415.13</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9969.780000000001</v>
+        <v>9969.27</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>22215.1</v>
+        <v>22213.96</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>44446.14</v>
+        <v>44247.4</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>28229.9</v>
+        <v>28254.22</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>40921.83</v>
+        <v>40957.09</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>30101.05</v>
+        <v>30126.98</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>37352.21</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6040.89</v>
+        <v>6065.84</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>52194.66</v>
+        <v>52050.69</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24461.13</v>
+        <v>24178.74</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>19138.85</v>
+        <v>18853.39</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>12572.46</v>
+        <v>12279.91</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>13119.85</v>
+        <v>12774.36</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>26544.56</v>
+        <v>26063.17</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8865.83</v>
+        <v>8628.43</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>11330.62</v>
+        <v>11426.78</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>32806.19</v>
+        <v>32751.34</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>65320.08</v>
+        <v>65210.86</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>34691.83</v>
+        <v>34633.82</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7628.05</v>
+        <v>7615.3</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>18531.92</v>
+        <v>18500.94</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>19906.5</v>
+        <v>20151.49</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6484.91</v>
+        <v>6564.73</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8795.98</v>
+        <v>8913.08</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>65304.87</v>
+        <v>66174.25</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>79667.35000000001</v>
+        <v>80706.98</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13064.96</v>
+        <v>13386.49</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>56588.09</v>
+        <v>57658.32</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>33191.39</v>
+        <v>33568.85</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>32207.31</v>
+        <v>32497.45</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7639.57</v>
+        <v>7688.43</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>13439.56</v>
+        <v>13359.01</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9825.18</v>
+        <v>9691.6</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>7472.85</v>
+        <v>7409.11</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5629.72</v>
+        <v>5672.37</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>14656.88</v>
+        <v>14712.41</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>23066.26</v>
+        <v>23008.02</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>13919.87</v>
+        <v>13884.72</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>14770.58</v>
+        <v>14910.91</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>18437.69</v>
+        <v>18575.05</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>41730.15</v>
+        <v>41313.99</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>9520.1</v>
+        <v>9478.370000000001</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>9180.18</v>
+        <v>9080.32</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>28750.92</v>
+        <v>28685.66</v>
       </c>
     </row>
     <row r="176">
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>28406.58</v>
+        <v>28336.43</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1375735-20-CM26</t>
+          <t>1210674-125-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11217,17 +11217,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>37877.19</v>
+        <v>18630.65</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1210674-125-CM26</t>
+          <t>1375735-20-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11278,17 +11278,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>18676.77</v>
+        <v>37783.66</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7096.43</v>
+        <v>7131.29</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>12111.37</v>
+        <v>12170.86</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>106544.88</v>
+        <v>106898.33</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>16703.89</v>
+        <v>16759.3</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>17109.45</v>
+        <v>17163.91</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>31613.93</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>27266.56</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>10249.43</v>
+        <v>10396.09</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>8599.92</v>
+        <v>8700.799999999999</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>20703.57</v>
+        <v>21053.72</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6115.89</v>
+        <v>6178.09</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>15776.5</v>
+        <v>15924.47</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>11892.39</v>
+        <v>12003.94</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>7635.22</v>
+        <v>7577.29</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>13003.42</v>
+        <v>12904.77</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>53124.9</v>
+        <v>52227.32</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7165.3</v>
+        <v>7063.61</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>8851.23</v>
+        <v>8729.610000000001</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>17288.05</v>
+        <v>17366.57</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>14705.05</v>
+        <v>14771.84</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5719.33</v>
+        <v>5804.49</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>57932.17</v>
+        <v>59033.55</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8327.690000000001</v>
+        <v>8385.18</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>19161.82</v>
+        <v>19294.12</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6770.76</v>
+        <v>6791.69</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>15232.96</v>
+        <v>15280.06</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>6593.48</v>
+        <v>6505.66</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7418.86</v>
+        <v>7273.64</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>10805.3</v>
+        <v>10645.21</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>15002.31</v>
+        <v>14693.99</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>16762.27</v>
+        <v>16921.49</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9987.85</v>
+        <v>10087.86</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>17052.64</v>
+        <v>17139.53</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>10219.36</v>
+        <v>10271.43</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>25467.24</v>
+        <v>25566.37</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>6410.92</v>
+        <v>6378.44</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7524.39</v>
+        <v>7540.43</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>51102.57</v>
+        <v>51211.49</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>29532.37</v>
+        <v>29595.31</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>54532.14</v>
+        <v>54648.37</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>6410.91</v>
+        <v>6452.7</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>63067.34</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>38411.35</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="222">
@@ -13997,13 +13997,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8655.68</v>
+        <v>8675.530000000001</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1211839-459-CM26</t>
+          <t>2766-453-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14028,12 +14028,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14058,13 +14058,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>36806.76</v>
+        <v>9795.67</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2766-453-CM26</t>
+          <t>1211839-459-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>9730.540000000001</v>
+        <v>37053.12</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6091.59</v>
+        <v>6134.22</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10421.99</v>
+        <v>10399.31</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7745.5</v>
+        <v>7728.65</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>10396.3</v>
+        <v>10373.68</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>200006.3</v>
+        <v>198848.63</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>63550.15</v>
+        <v>63182.31</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>8218.59</v>
+        <v>8085.96</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7988.99</v>
+        <v>7860.07</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>21179.27</v>
+        <v>20839.69</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>39255.8</v>
+        <v>38626.39</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>17649.08</v>
+        <v>17443.73</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>33634.43</v>
+        <v>33243.07</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>6398.11</v>
+        <v>6323.67</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>14500.04</v>
+        <v>14419.65</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,129 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5560.51</v>
+        <v>5529.68</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>3179-216-CM26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>9528.299999999999</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1393495-698-CM26</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>61.981.080-5</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>29414.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M492"/>
+  <dimension ref="A1:M505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1465,7 +1465,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1607-24-CM25</t>
+          <t>5705-1-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1505,32 +1505,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5518.03</v>
+        <v>7306.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5705-1-CM25</t>
+          <t>1607-24-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1550,17 +1546,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1570,22 +1566,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7306.09</v>
+        <v>5518.03</v>
       </c>
     </row>
     <row r="19">
@@ -1782,7 +1782,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2686-66-CM25</t>
+          <t>3439-1-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5730.77</v>
+        <v>6725.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3439-1-CM25</t>
+          <t>2686-66-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6725.48</v>
+        <v>5730.77</v>
       </c>
     </row>
     <row r="24">
@@ -2611,7 +2611,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5510-17-CM25</t>
+          <t>1075956-39-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2666,13 +2666,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>48736.32</v>
+        <v>46802.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1075956-39-CM25</t>
+          <t>5510-17-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2692,17 +2692,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>46802.49</v>
+        <v>48736.32</v>
       </c>
     </row>
     <row r="37">
@@ -5050,7 +5050,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3453-216-CM25</t>
+          <t>3453-215-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5109,13 +5109,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>12429.03</v>
+        <v>12762.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3453-215-CM25</t>
+          <t>3453-216-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>12762.56</v>
+        <v>12429.03</v>
       </c>
     </row>
     <row r="76">
@@ -5619,7 +5619,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1293138-143-CM25</t>
+          <t>1293138-144-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5659,26 +5659,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.070.635-1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12910.81</v>
+        <v>5950.69</v>
       </c>
     </row>
     <row r="84">
@@ -5810,7 +5806,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1293138-144-CM25</t>
+          <t>1293138-146-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5850,28 +5846,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5950.69</v>
+        <v>13457.17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1293138-146-CM25</t>
+          <t>1293138-143-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>13457.17</v>
+        <v>12910.81</v>
       </c>
     </row>
     <row r="88">
@@ -6322,7 +6322,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5153-1359-CM25</t>
+          <t>1293138-149-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6342,17 +6342,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.367.722-0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>30237.07</v>
+        <v>44852.29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1293138-152-CM25</t>
+          <t>5153-1359-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6407,17 +6407,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26761.09</v>
+        <v>30237.07</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1293138-149-CM25</t>
+          <t>1293138-152-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>44852.29</v>
+        <v>26761.09</v>
       </c>
     </row>
     <row r="97">
@@ -6834,7 +6834,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1217466-54-CM25</t>
+          <t>548874-137-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6854,17 +6854,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.905.003-9</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6874,26 +6874,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>16211.06</v>
+        <v>24951.94</v>
       </c>
     </row>
     <row r="103">
@@ -6964,7 +6960,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>548874-137-CM25</t>
+          <t>1217466-54-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6984,17 +6980,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.905.003-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7004,22 +7000,26 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>24951.94</v>
+        <v>16211.06</v>
       </c>
     </row>
     <row r="105">
@@ -7789,7 +7789,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1375757-25-CM25</t>
+          <t>1293138-186-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7848,13 +7848,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>22120.94</v>
+        <v>6295.88</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1293138-186-CM25</t>
+          <t>1375757-25-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6295.88</v>
+        <v>22120.94</v>
       </c>
     </row>
     <row r="119">
@@ -7984,7 +7984,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1360-77-CM25</t>
+          <t>2279-570-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.960.900-K</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8024,17 +8024,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMMERCE CHILE SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.037.031-0</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8043,13 +8043,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>20403.96</v>
+        <v>26514.31</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2279-570-CM25</t>
+          <t>1360-77-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.960.900-K</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8089,17 +8089,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMMERCE CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.037.031-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>26514.31</v>
+        <v>20403.96</v>
       </c>
     </row>
     <row r="122">
@@ -8423,7 +8423,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1375158-14-CM25</t>
+          <t>4794-110-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>15460.77</v>
+        <v>26166.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4794-110-CM25</t>
+          <t>1375158-14-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8539,13 +8539,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>26166.24</v>
+        <v>15460.77</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>256-1-CM25</t>
+          <t>1224957-781-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.559.762-5</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8604,13 +8604,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>25098.81</v>
+        <v>8329.77</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1224957-781-CM25</t>
+          <t>256-1-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8635,12 +8635,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.559.762-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8329.77</v>
+        <v>25098.81</v>
       </c>
     </row>
     <row r="131">
@@ -8805,7 +8805,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1211839-7467-CM25</t>
+          <t>1293138-180-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8864,13 +8864,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>44349.25</v>
+        <v>13062.12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1293138-180-CM25</t>
+          <t>1211839-7467-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>13062.12</v>
+        <v>44349.25</v>
       </c>
     </row>
     <row r="135">
@@ -9065,7 +9065,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2460-2228-CM25</t>
+          <t>4955-82-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9105,32 +9105,28 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6903.81</v>
+        <v>9895.99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4955-82-CM25</t>
+          <t>2460-2228-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9155,12 +9151,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9170,22 +9166,26 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9895.99</v>
+        <v>6903.81</v>
       </c>
     </row>
     <row r="139">
@@ -9508,7 +9508,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1460278-50-CM25</t>
+          <t>1057967-32-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9528,17 +9528,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9548,28 +9548,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ROMANESCU SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>77.199.251-K</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>15119.37</v>
+        <v>29182.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057967-32-CM25</t>
+          <t>94-164-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9589,17 +9593,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9609,32 +9613,28 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.050.859-4</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>29182.06</v>
+        <v>23621.32</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>94-164-CM25</t>
+          <t>1460278-50-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
+          <t>ROMANESCU SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.050.859-4</t>
+          <t>77.199.251-K</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9689,13 +9689,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>23621.32</v>
+        <v>15119.37</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1305544-365-CM25</t>
+          <t>2735-1160-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>10411.51</v>
+        <v>17519.73</v>
       </c>
     </row>
     <row r="148">
@@ -9821,7 +9821,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2735-1160-CM25</t>
+          <t>1305544-365-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>17519.73</v>
+        <v>10411.51</v>
       </c>
     </row>
     <row r="150">
@@ -10402,7 +10402,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>618-518-CM25</t>
+          <t>5178-3868-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10422,17 +10422,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10442,32 +10442,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6127.4</v>
+        <v>9421.719999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5178-3868-CM25</t>
+          <t>548875-155-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10492,12 +10488,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10507,28 +10503,32 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>9421.719999999999</v>
+        <v>38190.63</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>548875-155-CM25</t>
+          <t>618-518-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10548,17 +10548,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>38190.63</v>
+        <v>6127.4</v>
       </c>
     </row>
     <row r="161">
@@ -10971,7 +10971,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1233-110-CM25</t>
+          <t>2173-201-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>60.804.010-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11011,26 +11011,22 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5787.24</v>
+        <v>22722.3</v>
       </c>
     </row>
     <row r="168">
@@ -11101,7 +11097,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2173-201-CM25</t>
+          <t>1233-110-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11121,17 +11117,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.804.010-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11141,22 +11137,26 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>22722.3</v>
+        <v>5787.24</v>
       </c>
     </row>
     <row r="170">
@@ -11227,7 +11227,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1460278-88-CM25</t>
+          <t>1460278-90-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>VENTURE STORE SPA</t>
+          <t>ROMANESCU SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.733.054-5</t>
+          <t>77.199.251-K</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -11282,13 +11282,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>21043.95</v>
+        <v>16893.15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1460278-90-CM25</t>
+          <t>1460278-88-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ROMANESCU SPA</t>
+          <t>VENTURE STORE SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.199.251-K</t>
+          <t>76.733.054-5</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>16893.15</v>
+        <v>21043.95</v>
       </c>
     </row>
     <row r="173">
@@ -11727,7 +11727,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>622-503-CM25</t>
+          <t>1385462-130-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11767,22 +11767,26 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>25073.44</v>
+        <v>18619.88</v>
       </c>
     </row>
     <row r="180">
@@ -11849,7 +11853,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1385462-130-CM25</t>
+          <t>622-503-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11874,12 +11878,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11889,32 +11893,28 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.326-9</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>18619.88</v>
+        <v>25073.44</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1306643-621-CM25</t>
+          <t>5531-228-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11973,13 +11973,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5729.89</v>
+        <v>48097.66</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5531-228-CM25</t>
+          <t>1306643-621-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>48097.66</v>
+        <v>5729.89</v>
       </c>
     </row>
     <row r="184">
@@ -13011,7 +13011,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1293138-280-CM25</t>
+          <t>1293138-258-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13070,13 +13070,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>20832.94</v>
+        <v>74498.05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1100335-54-CM25</t>
+          <t>1293138-277-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13101,12 +13101,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13116,12 +13116,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>17525.41</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1293138-277-CM25</t>
+          <t>188-939-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13161,17 +13161,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8155</v>
+        <v>5955.62</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1293138-258-CM25</t>
+          <t>1100335-54-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13265,13 +13265,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>74498.05</v>
+        <v>17525.41</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>188-939-CM25</t>
+          <t>1293138-280-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13291,17 +13291,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13330,13 +13330,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5955.62</v>
+        <v>20832.94</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5510-116-CM25</t>
+          <t>1375754-44-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13356,17 +13356,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13376,28 +13376,32 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>55390.44</v>
+        <v>17940.68</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5178-4585-CM25</t>
+          <t>2580-1214-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13422,12 +13426,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13437,28 +13441,32 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>16253.79</v>
+        <v>10199.74</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1375754-44-CM25</t>
+          <t>5178-4585-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13483,12 +13491,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.981.260-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13498,32 +13506,28 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>17940.68</v>
+        <v>16253.79</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2580-1214-CM25</t>
+          <t>5510-116-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13543,17 +13547,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13563,26 +13567,22 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>10199.74</v>
+        <v>55390.44</v>
       </c>
     </row>
     <row r="208">
@@ -13905,7 +13905,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>577290-200-CM25</t>
+          <t>425-716-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13925,17 +13925,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.979.750-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13964,13 +13964,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>20827.8</v>
+        <v>14960.08</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>425-716-CM25</t>
+          <t>577290-200-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.979.750-7</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14029,13 +14029,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>14960.08</v>
+        <v>20827.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1271356-186-CM25</t>
+          <t>2377-261-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14060,12 +14060,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14094,13 +14094,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>51654.25</v>
+        <v>14685.22</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2377-261-CM25</t>
+          <t>1271356-186-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14125,12 +14125,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14140,12 +14140,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14159,7 +14159,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>14685.22</v>
+        <v>51654.25</v>
       </c>
     </row>
     <row r="217">
@@ -14230,7 +14230,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2452-3208-CM25</t>
+          <t>1293138-260-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14255,12 +14255,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14270,32 +14270,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>53340.87</v>
+        <v>98730.73</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1154491-8-CM25</t>
+          <t>2345-641-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14320,12 +14316,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.216.000-7</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14354,13 +14350,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>10766.76</v>
+        <v>21446.36</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5153-2309-CM25</t>
+          <t>1057049-23302-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14380,17 +14376,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14400,28 +14396,32 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>151081.97</v>
+        <v>7334.69</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1057049-23302-CM25</t>
+          <t>5153-2309-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14461,32 +14461,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.999.000-5</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>7334.69</v>
+        <v>151081.97</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2345-641-CM25</t>
+          <t>1154491-8-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14511,12 +14507,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.216.000-7</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14545,13 +14541,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>21446.36</v>
+        <v>10766.76</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1293138-260-CM25</t>
+          <t>2452-3208-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14576,12 +14572,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14591,22 +14587,26 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>98730.73</v>
+        <v>53340.87</v>
       </c>
     </row>
     <row r="224">
@@ -14799,12 +14799,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1305544-417-CM25</t>
+          <t>1385462-203-SE25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -14858,13 +14858,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>17690.59</v>
+        <v>78241.62</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1475044-13-CM25</t>
+          <t>758-907-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14904,28 +14904,32 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>12543.1</v>
+        <v>18501.24</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>758-907-CM25</t>
+          <t>1475044-13-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14950,12 +14954,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14965,37 +14969,33 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.744.548-2</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>18501.24</v>
+        <v>12543.1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1385462-203-SE25</t>
+          <t>1305544-417-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2239-3-LR23</t>
+          <t>2239-4-LR25</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -15015,12 +15015,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15030,12 +15030,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>78241.62</v>
+        <v>17690.59</v>
       </c>
     </row>
     <row r="231">
@@ -15120,7 +15120,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3474-788-CM25</t>
+          <t>598-318-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15145,12 +15145,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15160,32 +15160,28 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>13100.13</v>
+        <v>12495.33</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>598-318-CM25</t>
+          <t>1210674-239-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15210,12 +15206,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15225,12 +15221,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.744.548-2</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -15240,7 +15236,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>12495.33</v>
+        <v>11448.13</v>
       </c>
     </row>
     <row r="234">
@@ -15311,7 +15307,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1210674-239-CM25</t>
+          <t>3474-788-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15336,12 +15332,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15351,22 +15347,26 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>11448.13</v>
+        <v>13100.13</v>
       </c>
     </row>
     <row r="236">
@@ -15750,7 +15750,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1460278-223-CM25</t>
+          <t>5510-122-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15770,17 +15770,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15790,12 +15790,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15805,13 +15805,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>7120.29</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5510-122-CM25</t>
+          <t>1460278-223-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15831,17 +15831,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15866,7 +15866,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8757.98</v>
+        <v>7120.29</v>
       </c>
     </row>
     <row r="244">
@@ -16575,7 +16575,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5441-799-CM25</t>
+          <t>1293138-353-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16600,12 +16600,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16615,28 +16615,32 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>13685.61</v>
+        <v>24347.39</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1293138-353-CM25</t>
+          <t>5441-799-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16661,12 +16665,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16676,26 +16680,22 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>24347.39</v>
+        <v>13685.61</v>
       </c>
     </row>
     <row r="257">
@@ -16827,7 +16827,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1057499-636-CM25</t>
+          <t>1057500-763-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16852,12 +16852,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16867,12 +16867,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -16886,13 +16886,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>21821.81</v>
+        <v>7899.53</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1057500-763-CM25</t>
+          <t>1057499-636-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>7899.53</v>
+        <v>21821.81</v>
       </c>
     </row>
     <row r="261">
@@ -17083,7 +17083,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1177296-555-CM25</t>
+          <t>1736-4055-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17123,22 +17123,26 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>13871.56</v>
+        <v>26260.93</v>
       </c>
     </row>
     <row r="264">
@@ -17205,7 +17209,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1736-4055-CM25</t>
+          <t>1177296-555-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17230,12 +17234,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17245,26 +17249,22 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.326-9</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>26260.93</v>
+        <v>13871.56</v>
       </c>
     </row>
     <row r="266">
@@ -18164,7 +18164,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5153-2715-CM25</t>
+          <t>4629-822-CM25</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18184,17 +18184,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18204,32 +18204,28 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.042.830-9</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>64098.29</v>
+        <v>14019.99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>634-1131-CM25</t>
+          <t>5153-2715-CM25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18249,17 +18245,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18269,12 +18265,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18288,13 +18284,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>28788.84</v>
+        <v>64098.29</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4629-822-CM25</t>
+          <t>634-1131-CM25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18319,12 +18315,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18334,28 +18330,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>14019.99</v>
+        <v>28788.84</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1016414-189-CM25</t>
+          <t>1385462-296-CM25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18380,12 +18380,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18395,12 +18395,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -18414,13 +18414,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>7781.62</v>
+        <v>37006.46</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1186229-388-CM25</t>
+          <t>1016414-189-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18460,28 +18460,32 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>78484.67999999999</v>
+        <v>7781.62</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1385462-296-CM25</t>
+          <t>1186229-388-CM25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18506,12 +18510,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18521,26 +18525,22 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.007.474-8</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>37006.46</v>
+        <v>78484.67999999999</v>
       </c>
     </row>
     <row r="286">
@@ -19680,7 +19680,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>692271-1-CM26</t>
+          <t>188-15-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19700,17 +19700,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19720,28 +19720,32 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>89.812.000-7</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>23911.07</v>
+        <v>24689.2</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>188-15-CM26</t>
+          <t>692271-1-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19761,17 +19765,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19781,26 +19785,22 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>89.812.000-7</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>24689.2</v>
+        <v>23911.07</v>
       </c>
     </row>
     <row r="306">
@@ -20302,7 +20302,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>564953-40-CM26</t>
+          <t>5067-217-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20322,17 +20322,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20342,12 +20342,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>JAIME DEIK Y CIA. LIMITADA</t>
+          <t>TAZ S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.450.030-k</t>
+          <t>96.891.420-0</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -20357,13 +20357,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>65963.37</v>
+        <v>6963.95</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5067-217-CM26</t>
+          <t>564953-40-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20383,17 +20383,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>TAZ S A</t>
+          <t>JAIME DEIK Y CIA. LIMITADA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>96.891.420-0</t>
+          <t>76.450.030-k</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -20418,7 +20418,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>6963.95</v>
+        <v>65963.37</v>
       </c>
     </row>
     <row r="316">
@@ -20611,7 +20611,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5520-70-CM26</t>
+          <t>1389488-86-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20636,12 +20636,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20651,28 +20651,32 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>15156.27</v>
+        <v>24466.16</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1389488-86-CM26</t>
+          <t>5520-70-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20697,12 +20701,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.981.320-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20712,26 +20716,22 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>24466.16</v>
+        <v>15156.27</v>
       </c>
     </row>
     <row r="321">
@@ -21188,7 +21188,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1475044-22-CM26</t>
+          <t>1475044-20-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21228,12 +21228,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>40733.54</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5621-56-CM26</t>
+          <t>1475044-22-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21289,32 +21289,28 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>6775.1</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1475044-20-CM26</t>
+          <t>5621-56-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21354,22 +21350,26 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>45222.5</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="331">
@@ -21826,7 +21826,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5684-100-CM26</t>
+          <t>1375757-57-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21866,28 +21866,32 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>10780.71</v>
+        <v>38859.55</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1375757-57-CM26</t>
+          <t>5684-100-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21912,12 +21916,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21927,26 +21931,22 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>38859.55</v>
+        <v>10780.71</v>
       </c>
     </row>
     <row r="340">
@@ -22330,7 +22330,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5510-18-CM26</t>
+          <t>5169-5-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -22370,32 +22370,28 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>89.812.000-7</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>11396.06</v>
+        <v>40593.49</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5169-5-CM26</t>
+          <t>5510-18-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22415,7 +22411,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -22435,22 +22431,26 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Articulos Deportivos Gacitua y Cia. Ltda</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>89.812.000-7</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>40593.49</v>
+        <v>11396.06</v>
       </c>
     </row>
     <row r="348">
@@ -22773,7 +22773,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2345-101-CM26</t>
+          <t>1475044-43-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22793,17 +22793,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22813,26 +22813,22 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>28254.22</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="354">
@@ -22899,7 +22895,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1475050-26-CM26</t>
+          <t>2345-101-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22919,17 +22915,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22939,28 +22935,32 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>30126.98</v>
+        <v>28254.22</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1475044-43-CM26</t>
+          <t>1475050-26-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>37384.39</v>
+        <v>30126.98</v>
       </c>
     </row>
     <row r="357">
@@ -23590,7 +23590,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>697058-25-CM26</t>
+          <t>642028-20-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23649,13 +23649,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>7615.3</v>
+        <v>32751.34</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>707429-41-CM26</t>
+          <t>5169-9-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23680,12 +23680,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23695,26 +23695,22 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>34633.82</v>
+        <v>65210.86</v>
       </c>
     </row>
     <row r="368">
@@ -23785,7 +23781,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5169-9-CM26</t>
+          <t>697058-25-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23810,12 +23806,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23825,28 +23821,32 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>65210.86</v>
+        <v>7615.3</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>642028-20-CM26</t>
+          <t>707429-41-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23886,12 +23886,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -23905,7 +23905,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>32751.34</v>
+        <v>34633.82</v>
       </c>
     </row>
     <row r="371">
@@ -25236,7 +25236,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1210674-125-CM26</t>
+          <t>5178-2120-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25261,12 +25261,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25276,12 +25276,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -25295,13 +25295,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>18630.65</v>
+        <v>28336.43</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5178-2120-CM26</t>
+          <t>1210674-125-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25326,12 +25326,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25341,12 +25341,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25360,13 +25360,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>28336.43</v>
+        <v>18630.65</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1057491-3099-CM26</t>
+          <t>1375746-62-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25391,12 +25391,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25406,32 +25406,28 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K394" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>7131.29</v>
+        <v>12170.86</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1375746-62-CM26</t>
+          <t>1057491-3099-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25456,12 +25452,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25471,28 +25467,32 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>12170.86</v>
+        <v>7131.29</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2173-112-CM26</t>
+          <t>2184-150-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25547,13 +25547,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>106898.33</v>
+        <v>16759.3</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2184-150-CM26</t>
+          <t>2173-112-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>16759.3</v>
+        <v>106898.33</v>
       </c>
     </row>
     <row r="398">
@@ -25675,7 +25675,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5510-54-CM26</t>
+          <t>5510-55-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25734,13 +25734,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>31782.04</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5510-55-CM26</t>
+          <t>5510-54-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25799,7 +25799,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>27411.55</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="401">
@@ -26183,7 +26183,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>3453-221-CM26</t>
+          <t>4642-586-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -26238,13 +26238,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>7577.29</v>
+        <v>12904.77</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>4642-586-CM26</t>
+          <t>3453-221-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>60.514.000-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -26299,7 +26299,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>12904.77</v>
+        <v>7577.29</v>
       </c>
     </row>
     <row r="409">
@@ -26748,7 +26748,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1499887-473-CM26</t>
+          <t>1499887-471-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -26803,13 +26803,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>19294.12</v>
+        <v>8385.18</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1499887-471-CM26</t>
+          <t>1499887-473-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>8385.18</v>
+        <v>19294.12</v>
       </c>
     </row>
     <row r="418">
@@ -27638,7 +27638,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>593951-200-CM26</t>
+          <t>2069-6355-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -27663,12 +27663,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -27678,26 +27678,22 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>7540.43</v>
+        <v>29595.31</v>
       </c>
     </row>
     <row r="431">
@@ -27764,7 +27760,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2069-6355-CM26</t>
+          <t>593951-200-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -27789,12 +27785,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -27804,22 +27800,26 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K432" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>29595.31</v>
+        <v>7540.43</v>
       </c>
     </row>
     <row r="433">
@@ -27886,7 +27886,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>5510-66-CM26</t>
+          <t>5510-65-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -27941,13 +27941,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>38661.76</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>552975-407-CM26</t>
+          <t>5510-66-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K435" t="inlineStr"/>
@@ -28002,13 +28002,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>6452.7</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5510-65-CM26</t>
+          <t>552975-407-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28033,12 +28033,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -28048,12 +28048,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K436" t="inlineStr"/>
@@ -28063,7 +28063,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>63478.5</v>
+        <v>6452.7</v>
       </c>
     </row>
     <row r="437">
@@ -29069,7 +29069,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1455288-224-CM26</t>
+          <t>2201-512-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29094,12 +29094,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.602.117-6</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>INSTITUTO NACIONAL DE REHABILITACION PEDRO AGUIRRE CERDA</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29109,12 +29109,12 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>INVERSIONES JIMENEZ SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>77.316.878-4</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K453" t="inlineStr"/>
@@ -29124,13 +29124,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>14419.65</v>
+        <v>5529.68</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2201-512-CM26</t>
+          <t>1455288-224-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29155,12 +29155,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.602.117-6</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE REHABILITACION PEDRO AGUIRRE CERDA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29170,12 +29170,12 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>INVERSIONES JIMENEZ SPA</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>77.316.878-4</t>
         </is>
       </c>
       <c r="K454" t="inlineStr"/>
@@ -29185,13 +29185,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>5529.68</v>
+        <v>14419.65</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>3179-216-CM26</t>
+          <t>1260-105-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29216,12 +29216,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29231,32 +29231,28 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>9528.299999999999</v>
+        <v>20916.48</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1260-105-CM26</t>
+          <t>3179-216-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29281,12 +29277,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -29296,22 +29292,26 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K456" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>20916.48</v>
+        <v>9528.299999999999</v>
       </c>
     </row>
     <row r="457">
@@ -29447,7 +29447,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2561-277-CM26</t>
+          <t>2561-275-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29506,13 +29506,13 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>10524.26</v>
+        <v>42110.68</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2561-275-CM26</t>
+          <t>1431841-897-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -29532,17 +29532,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>61.004.035-7</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -29552,12 +29552,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
@@ -29571,7 +29571,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>42110.68</v>
+        <v>26227.76</v>
       </c>
     </row>
     <row r="461">
@@ -29642,7 +29642,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1431841-897-CM26</t>
+          <t>2561-277-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -29662,17 +29662,17 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.004.035-7</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -29682,12 +29682,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -29701,13 +29701,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>26227.76</v>
+        <v>10524.26</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>5153-1382-CM26</t>
+          <t>1057491-4657-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -29727,17 +29727,17 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -29747,12 +29747,12 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -29766,7 +29766,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>16760.75</v>
+        <v>8579.309999999999</v>
       </c>
     </row>
     <row r="464">
@@ -29837,7 +29837,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>1057491-4657-CM26</t>
+          <t>5153-1382-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -29857,17 +29857,17 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -29877,12 +29877,12 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -29896,7 +29896,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>8579.309999999999</v>
+        <v>16760.75</v>
       </c>
     </row>
     <row r="466">
@@ -30028,7 +30028,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1210674-184-CM26</t>
+          <t>1306643-282-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30048,17 +30048,17 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -30068,12 +30068,12 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -30087,13 +30087,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>32898.81</v>
+        <v>28144.8</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1306643-282-CM26</t>
+          <t>1210674-184-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30113,17 +30113,17 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30133,12 +30133,12 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -30152,7 +30152,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>28144.8</v>
+        <v>32898.81</v>
       </c>
     </row>
     <row r="470">
@@ -30223,7 +30223,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>5067-1772-CM26</t>
+          <t>1485217-125-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30243,17 +30243,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -30263,28 +30263,32 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
-        </is>
-      </c>
-      <c r="K471" t="inlineStr"/>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>68935.75999999999</v>
+        <v>7119.07</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1485217-125-CM26</t>
+          <t>5067-1772-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30304,17 +30308,17 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30324,26 +30328,22 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
-        </is>
-      </c>
-      <c r="K472" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.675.854-1</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>7119.07</v>
+        <v>68935.75999999999</v>
       </c>
     </row>
     <row r="473">
@@ -30796,7 +30796,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2345-434-CM26</t>
+          <t>1867-228-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30821,12 +30821,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30836,32 +30836,28 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>35843.37</v>
+        <v>9495.08</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1867-228-CM26</t>
+          <t>2345-434-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -30886,12 +30882,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -30901,22 +30897,26 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K481" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>9495.08</v>
+        <v>35843.37</v>
       </c>
     </row>
     <row r="482">
@@ -31072,7 +31072,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -31608,6 +31608,823 @@
       </c>
       <c r="M492" s="2" t="n">
         <v>12845.81</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>5441-489-CM26</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M493" s="2" t="n">
+        <v>37378.86</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2682-375-CM26</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>69.255.500-7</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M494" s="2" t="n">
+        <v>13839.93</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>4629-222-CM26</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>61.502.000-1</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>DIRECCION DEL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M495" s="2" t="n">
+        <v>6205.79</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>4794-103-CM26</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M496" s="2" t="n">
+        <v>25721.1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>629373-275-CM26</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>70.962.500-4</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M497" s="2" t="n">
+        <v>45132.22</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>5640-57-CM26</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="n">
+        <v>58487.38</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>5640-56-CM26</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M499" s="2" t="n">
+        <v>58999.19</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>1475044-78-CM26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M500" s="2" t="n">
+        <v>60463.1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>4794-104-CM26</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>INTERGROUPE S.A.</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M501" s="2" t="n">
+        <v>60771.52</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>1436733-158-CM26</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>61.981.060-0</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="n">
+        <v>6764.94</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>5529-105-CM26</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="n">
+        <v>7994.81</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>593951-250-CM26</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="n">
+        <v>141171.63</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>5482-207-CM26</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>69.070.500-1</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M505" s="2" t="n">
+        <v>12783.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M508"/>
+  <dimension ref="A1:M510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9886,7 +9886,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1305544-365-CM25</t>
+          <t>2735-1160-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10411.51</v>
+        <v>17519.73</v>
       </c>
     </row>
     <row r="151">
@@ -10012,7 +10012,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2735-1160-CM25</t>
+          <t>1305544-365-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>17519.73</v>
+        <v>10411.51</v>
       </c>
     </row>
     <row r="153">
@@ -12946,7 +12946,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5251-1650-CM25</t>
+          <t>1293138-270-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12986,22 +12986,26 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>77.367.722-0</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7549.49</v>
+        <v>22850.61</v>
       </c>
     </row>
     <row r="199">
@@ -13137,7 +13141,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1293138-270-CM25</t>
+          <t>5251-1650-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13162,12 +13166,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13177,26 +13181,22 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.526.830-8</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>22850.61</v>
+        <v>7549.49</v>
       </c>
     </row>
     <row r="202">
@@ -21379,7 +21379,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1475044-20-CM26</t>
+          <t>5621-56-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21419,28 +21419,32 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>45222.5</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1475044-22-CM26</t>
+          <t>1475044-20-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21480,12 +21484,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21495,13 +21499,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>40733.54</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5621-56-CM26</t>
+          <t>1475044-22-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21541,26 +21545,22 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6775.1</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="334">
@@ -22017,7 +22017,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1375757-57-CM26</t>
+          <t>1057973-1-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22042,12 +22042,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22057,26 +22057,22 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>38859.55</v>
+        <v>13145.81</v>
       </c>
     </row>
     <row r="342">
@@ -22143,7 +22139,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1057973-1-CM26</t>
+          <t>1375757-57-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22168,12 +22164,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22183,22 +22179,26 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>13145.81</v>
+        <v>38859.55</v>
       </c>
     </row>
     <row r="344">
@@ -22964,7 +22964,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1475044-43-CM26</t>
+          <t>5169-7-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23019,13 +23019,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>37384.39</v>
+        <v>40957.09</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5169-7-CM26</t>
+          <t>2345-101-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23045,17 +23045,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23065,28 +23065,32 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>40957.09</v>
+        <v>28254.22</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2345-101-CM26</t>
+          <t>1475044-43-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23106,17 +23110,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23126,26 +23130,22 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.719.470-6</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>28254.22</v>
+        <v>37384.39</v>
       </c>
     </row>
     <row r="359">
@@ -23972,7 +23972,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>697058-25-CM26</t>
+          <t>707429-41-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23997,12 +23997,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -24031,13 +24031,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>7615.3</v>
+        <v>34633.82</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>707429-41-CM26</t>
+          <t>697058-25-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24062,12 +24062,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24077,12 +24077,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -24096,7 +24096,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>34633.82</v>
+        <v>7615.3</v>
       </c>
     </row>
     <row r="374">
@@ -25557,7 +25557,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1375746-62-CM26</t>
+          <t>1057491-3099-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25582,12 +25582,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25597,28 +25597,32 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>12170.86</v>
+        <v>7131.29</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1057491-3099-CM26</t>
+          <t>1375746-62-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25643,12 +25647,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25658,26 +25662,22 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>7131.29</v>
+        <v>12170.86</v>
       </c>
     </row>
     <row r="399">
@@ -25866,7 +25866,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>5510-55-CM26</t>
+          <t>5510-54-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25925,13 +25925,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>27411.55</v>
+        <v>31782.04</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5510-54-CM26</t>
+          <t>5510-55-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>31782.04</v>
+        <v>27411.55</v>
       </c>
     </row>
     <row r="404">
@@ -26374,7 +26374,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4642-586-CM26</t>
+          <t>3453-221-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>60.514.000-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -26429,13 +26429,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>12904.77</v>
+        <v>7577.29</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>3453-221-CM26</t>
+          <t>4642-586-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -26490,7 +26490,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>7577.29</v>
+        <v>12904.77</v>
       </c>
     </row>
     <row r="412">
@@ -27061,7 +27061,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5520-3737-CM26</t>
+          <t>5647-107-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27101,32 +27101,28 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>6791.69</v>
+        <v>15280.06</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5647-107-CM26</t>
+          <t>5520-3737-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27166,22 +27162,26 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K422" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>15280.06</v>
+        <v>6791.69</v>
       </c>
     </row>
     <row r="423">
@@ -27890,7 +27890,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>5510-63-CM26</t>
+          <t>593951-200-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -27910,17 +27910,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -27930,28 +27930,32 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>51211.49</v>
+        <v>7540.43</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>593951-200-CM26</t>
+          <t>5510-64-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -27971,17 +27975,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27991,32 +27995,28 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>7540.43</v>
+        <v>54648.37</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5510-64-CM26</t>
+          <t>5510-63-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28071,13 +28071,13 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>54648.37</v>
+        <v>51211.49</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5510-65-CM26</t>
+          <t>552975-407-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28102,12 +28102,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28117,12 +28117,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K437" t="inlineStr"/>
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>63478.5</v>
+        <v>6452.7</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>5510-66-CM26</t>
+          <t>5510-65-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -28193,13 +28193,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>38661.76</v>
+        <v>63478.5</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>552975-407-CM26</t>
+          <t>5510-66-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28224,12 +28224,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28239,12 +28239,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K439" t="inlineStr"/>
@@ -28254,7 +28254,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>6452.7</v>
+        <v>38661.76</v>
       </c>
     </row>
     <row r="440">
@@ -28573,7 +28573,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1460278-299-CM26</t>
+          <t>1217466-80-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -28593,17 +28593,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.905.003-9</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -28632,13 +28632,13 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>7728.65</v>
+        <v>10373.68</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1217466-80-CM26</t>
+          <t>1460278-299-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -28658,17 +28658,17 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>60.905.003-9</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>10373.68</v>
+        <v>7728.65</v>
       </c>
     </row>
     <row r="447">
@@ -28825,7 +28825,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1305552-89-CM26</t>
+          <t>1057049-17017-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -28865,28 +28865,32 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K449" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>8085.96</v>
+        <v>7860.07</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1057049-17017-CM26</t>
+          <t>1305552-89-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -28911,12 +28915,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -28926,26 +28930,22 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>7860.07</v>
+        <v>8085.96</v>
       </c>
     </row>
     <row r="451">
@@ -29073,7 +29073,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1655-230-CM26</t>
+          <t>3179-224-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29093,17 +29093,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29113,12 +29113,12 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K453" t="inlineStr"/>
@@ -29128,7 +29128,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>8832.34</v>
+        <v>6323.67</v>
       </c>
     </row>
     <row r="454">
@@ -29199,7 +29199,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>3179-224-CM26</t>
+          <t>1655-230-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29219,17 +29219,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29239,12 +29239,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K455" t="inlineStr"/>
@@ -29254,7 +29254,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>6323.67</v>
+        <v>8832.34</v>
       </c>
     </row>
     <row r="456">
@@ -29703,7 +29703,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>1431841-897-CM26</t>
+          <t>2561-277-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -29723,17 +29723,17 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.004.035-7</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -29743,12 +29743,12 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -29762,13 +29762,13 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>26227.76</v>
+        <v>10524.26</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2274-116-CM26</t>
+          <t>1431841-897-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -29788,17 +29788,17 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -29808,12 +29808,12 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -29827,13 +29827,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>17982.65</v>
+        <v>26227.76</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2561-277-CM26</t>
+          <t>2274-116-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -29858,12 +29858,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.004.035-7</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -29873,12 +29873,12 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -29892,7 +29892,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>10524.26</v>
+        <v>17982.65</v>
       </c>
     </row>
     <row r="466">
@@ -30735,7 +30735,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>948354-1407-CM26</t>
+          <t>1736-898-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -30760,12 +30760,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -30775,28 +30775,32 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>TAZ S A</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>96.891.420-0</t>
-        </is>
-      </c>
-      <c r="K479" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>11095.48</v>
+        <v>20402.95</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1736-898-CM26</t>
+          <t>948354-1407-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30821,12 +30825,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30836,26 +30840,22 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>TAZ S A</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.891.420-0</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>20402.95</v>
+        <v>11095.48</v>
       </c>
     </row>
     <row r="481">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -31865,7 +31865,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2682-375-CM26</t>
+          <t>4629-222-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -31890,12 +31890,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -31924,13 +31924,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>13839.93</v>
+        <v>6205.79</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4629-222-CM26</t>
+          <t>2682-375-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -31955,12 +31955,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -31989,7 +31989,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>6205.79</v>
+        <v>13839.93</v>
       </c>
     </row>
     <row r="499">
@@ -32121,7 +32121,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5640-57-CM26</t>
+          <t>1057882-13-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -32146,12 +32146,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -32161,12 +32161,12 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K501" t="inlineStr"/>
@@ -32176,13 +32176,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>58487.38</v>
+        <v>15221.28</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>5640-56-CM26</t>
+          <t>5640-57-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32237,13 +32237,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>58999.19</v>
+        <v>58487.38</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1475044-78-CM26</t>
+          <t>5640-56-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -32298,13 +32298,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>60463.1</v>
+        <v>58999.19</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>4794-104-CM26</t>
+          <t>1475044-78-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32359,13 +32359,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>60771.52</v>
+        <v>60463.1</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1436733-158-CM26</t>
+          <t>4794-104-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -32390,12 +32390,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>61.981.060-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -32405,12 +32405,12 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K505" t="inlineStr"/>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>6764.94</v>
+        <v>60771.52</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>5529-105-CM26</t>
+          <t>1436733-158-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -32451,12 +32451,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.060-0</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -32466,32 +32466,28 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K506" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>7994.81</v>
+        <v>6764.94</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>593951-250-CM26</t>
+          <t>5529-105-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -32516,12 +32512,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32531,12 +32527,12 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -32550,71 +32546,197 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>141171.63</v>
+        <v>7994.81</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
+          <t>758-812-CM26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>60.509.001-k</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="n">
+        <v>17156.05</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>593951-250-CM26</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M509" s="2" t="n">
+        <v>141171.63</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
           <t>5482-207-CM26</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr">
+      <c r="D510" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr">
+      <c r="E510" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr">
+      <c r="F510" t="inlineStr">
         <is>
           <t>69.070.500-1</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr">
+      <c r="G510" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I508" t="inlineStr">
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
+      <c r="J510" t="inlineStr">
         <is>
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L508" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M508" s="2" t="n">
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="n">
         <v>12783.28</v>
       </c>
     </row>
